--- a/BVSimulationFiles/84.xlsx
+++ b/BVSimulationFiles/84.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009236947791164656</v>
+        <v>0.001847389558232931</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009232092332596417</v>
+        <v>0.001846418466519283</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009227239426329914</v>
+        <v>0.001845447885265983</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009222389071023519</v>
+        <v>0.001844477814204704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009217541265336298</v>
+        <v>0.00184350825306726</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009212696007928037</v>
+        <v>0.001842539201585607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0009207853297459209</v>
+        <v>0.001841570659491842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009203013132591004</v>
+        <v>0.001840602626518201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009198175511985308</v>
+        <v>0.001839635102397062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009193340434304717</v>
+        <v>0.001838668086860943</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009188507898212523</v>
+        <v>0.001837701579642505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0009183677902372731</v>
+        <v>0.001836735580474546</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0009178850445450034</v>
+        <v>0.001835770089090007</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000917402552610984</v>
+        <v>0.001834805105221968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009169203143018251</v>
+        <v>0.00183384062860365</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0009164383294842072</v>
+        <v>0.001832876658968414</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009159565980248808</v>
+        <v>0.001831913196049762</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009154751197906672</v>
+        <v>0.001830950239581334</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000914993894648456</v>
+        <v>0.001829987789296912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009145129224652086</v>
+        <v>0.001829025844930417</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009236947791164656</v>
+        <v>0.001847389558232931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009232092332596417</v>
+        <v>0.001846418466519283</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009227239426329914</v>
+        <v>0.001845447885265983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009222389071023519</v>
+        <v>0.001844477814204704</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009217541265336298</v>
+        <v>0.00184350825306726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009212696007928037</v>
+        <v>0.001842539201585607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009207853297459209</v>
+        <v>0.001841570659491842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009203013132591004</v>
+        <v>0.001840602626518201</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009198175511985308</v>
+        <v>0.001839635102397062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009193340434304717</v>
+        <v>0.001838668086860943</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009188507898212523</v>
+        <v>0.001837701579642505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009183677902372731</v>
+        <v>0.001836735580474546</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009178850445450034</v>
+        <v>0.001835770089090007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000917402552610984</v>
+        <v>0.001834805105221968</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009169203143018251</v>
+        <v>0.00183384062860365</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009164383294842072</v>
+        <v>0.001832876658968414</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009159565980248808</v>
+        <v>0.001831913196049762</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009154751197906672</v>
+        <v>0.001830950239581334</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000914993894648456</v>
+        <v>0.001829987789296912</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009145129224652086</v>
+        <v>0.001829025844930417</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/84.xlsx
+++ b/BVSimulationFiles/84.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001847389558232931</v>
+        <v>0.01847389558232931</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001846418466519283</v>
+        <v>0.01846418466519283</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001845447885265983</v>
+        <v>0.01845447885265983</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001844477814204704</v>
+        <v>0.01844477814204704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00184350825306726</v>
+        <v>0.0184350825306726</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001842539201585607</v>
+        <v>0.01842539201585607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001841570659491842</v>
+        <v>0.01841570659491842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001840602626518201</v>
+        <v>0.01840602626518201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001839635102397062</v>
+        <v>0.01839635102397062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001838668086860943</v>
+        <v>0.01838668086860943</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001837701579642505</v>
+        <v>0.01837701579642505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001836735580474546</v>
+        <v>0.01836735580474546</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001835770089090007</v>
+        <v>0.01835770089090007</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001834805105221968</v>
+        <v>0.01834805105221968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00183384062860365</v>
+        <v>0.0183384062860365</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001832876658968414</v>
+        <v>0.01832876658968414</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001831913196049762</v>
+        <v>0.01831913196049762</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001830950239581334</v>
+        <v>0.01830950239581334</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001829987789296912</v>
+        <v>0.01829987789296912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001829025844930417</v>
+        <v>0.01829025844930417</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001847389558232931</v>
+        <v>0.01847389558232931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001846418466519283</v>
+        <v>0.01846418466519283</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001845447885265983</v>
+        <v>0.01845447885265983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001844477814204704</v>
+        <v>0.01844477814204704</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00184350825306726</v>
+        <v>0.0184350825306726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001842539201585607</v>
+        <v>0.01842539201585607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001841570659491842</v>
+        <v>0.01841570659491842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001840602626518201</v>
+        <v>0.01840602626518201</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001839635102397062</v>
+        <v>0.01839635102397062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001838668086860943</v>
+        <v>0.01838668086860943</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001837701579642505</v>
+        <v>0.01837701579642505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001836735580474546</v>
+        <v>0.01836735580474546</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001835770089090007</v>
+        <v>0.01835770089090007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001834805105221968</v>
+        <v>0.01834805105221968</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00183384062860365</v>
+        <v>0.0183384062860365</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001832876658968414</v>
+        <v>0.01832876658968414</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001831913196049762</v>
+        <v>0.01831913196049762</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001830950239581334</v>
+        <v>0.01830950239581334</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001829987789296912</v>
+        <v>0.01829987789296912</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001829025844930417</v>
+        <v>0.01829025844930417</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/84.xlsx
+++ b/BVSimulationFiles/84.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002227368421052632</v>
+        <v>0.001459310344827586</v>
       </c>
       <c r="D1" t="n">
-        <v>0.004454736842105264</v>
+        <v>0.002918620689655173</v>
       </c>
       <c r="E1" t="n">
-        <v>0.006682105263157895</v>
+        <v>0.004377931034482758</v>
       </c>
       <c r="F1" t="n">
-        <v>0.008909473684210528</v>
+        <v>0.005837241379310345</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01113684210526316</v>
+        <v>0.007296551724137932</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01336421052631579</v>
+        <v>0.008755862068965517</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01559157894736842</v>
+        <v>0.0102151724137931</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01781894736842106</v>
+        <v>0.01167448275862069</v>
       </c>
       <c r="K1" t="n">
-        <v>0.02004631578947369</v>
+        <v>0.01313379310344828</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02227368421052632</v>
+        <v>0.01459310344827586</v>
       </c>
       <c r="M1" t="n">
-        <v>0.02450105263157895</v>
+        <v>0.01605241379310345</v>
       </c>
       <c r="N1" t="n">
-        <v>0.02672842105263158</v>
+        <v>0.01751172413793103</v>
       </c>
       <c r="O1" t="n">
-        <v>0.02895578947368422</v>
+        <v>0.01897103448275862</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03118315789473685</v>
+        <v>0.02043034482758621</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.03341052631578947</v>
+        <v>0.0218896551724138</v>
       </c>
       <c r="R1" t="n">
-        <v>0.03563789473684211</v>
+        <v>0.02334896551724138</v>
       </c>
       <c r="S1" t="n">
-        <v>0.03786526315789474</v>
+        <v>0.02480827586206897</v>
       </c>
       <c r="T1" t="n">
-        <v>0.04009263157894737</v>
+        <v>0.02626758620689655</v>
       </c>
       <c r="U1" t="n">
+        <v>0.02772689655172414</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.02918620689655173</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.03064551724137931</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.0321048275862069</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.03356413793103449</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.03502344827586207</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.03648275862068966</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.03794206896551724</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.03940137931034483</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.04086068965517241</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01847389558232931</v>
+        <v>0.05904039759219354</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01846418466519283</v>
+        <v>0.05899973442464881</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01845447885265983</v>
+        <v>0.05895909926323654</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01844477814204704</v>
+        <v>0.05891849208866792</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0184350825306726</v>
+        <v>0.05887791288166744</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01842539201585607</v>
+        <v>0.05883736162297289</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01841570659491842</v>
+        <v>0.05879683829333526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01840602626518201</v>
+        <v>0.0587563428735189</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01839635102397062</v>
+        <v>0.05871587534430128</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01838668086860943</v>
+        <v>0.05867543568647321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01837701579642505</v>
+        <v>0.05863502388083874</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01836735580474546</v>
+        <v>0.05859463990821502</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01835770089090007</v>
+        <v>0.05855428374943254</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01834805105221968</v>
+        <v>0.05851395538533498</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0183384062860365</v>
+        <v>0.05847365479677909</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01832876658968414</v>
+        <v>0.05843338196463493</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01831913196049762</v>
+        <v>0.05839313686978573</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01830950239581334</v>
+        <v>0.05835291949312784</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01829987789296912</v>
+        <v>0.05831272981557074</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01829025844930417</v>
+        <v>0.05827256781803713</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.05823243348146282</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.05819232678679673</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05815224771500098</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.05811219624705066</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0580721723639341</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.05803217604665262</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.05799220727622074</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.05795226603366595</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.05791235230002886</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.0578724660563631</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01847389558232931</v>
+        <v>0.05904039759219354</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01846418466519283</v>
+        <v>0.05899973442464881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01845447885265983</v>
+        <v>0.05895909926323654</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01844477814204704</v>
+        <v>0.05891849208866792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0184350825306726</v>
+        <v>0.05887791288166744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01842539201585607</v>
+        <v>0.05883736162297289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01841570659491842</v>
+        <v>0.05879683829333526</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01840602626518201</v>
+        <v>0.0587563428735189</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01839635102397062</v>
+        <v>0.05871587534430128</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01838668086860943</v>
+        <v>0.05867543568647321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01837701579642505</v>
+        <v>0.05863502388083874</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01836735580474546</v>
+        <v>0.05859463990821502</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01835770089090007</v>
+        <v>0.05855428374943254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01834805105221968</v>
+        <v>0.05851395538533498</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0183384062860365</v>
+        <v>0.05847365479677909</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01832876658968414</v>
+        <v>0.05843338196463493</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01831913196049762</v>
+        <v>0.05839313686978573</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01830950239581334</v>
+        <v>0.05835291949312784</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01829987789296912</v>
+        <v>0.05831272981557074</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01829025844930417</v>
+        <v>0.05827256781803713</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.05823243348146282</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.05819232678679673</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.05815224771500098</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.05811219624705066</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0580721723639341</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05803217604665262</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.05799220727622074</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.05795226603366595</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.05791235230002886</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.0578724660563631</v>
       </c>
     </row>
   </sheetData>
